--- a/saidas/historico_runs/historico_runs_2026_07_28.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_07_28.xlsx
@@ -4427,7 +4427,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -4436,25 +4436,25 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>0.103</v>
+        <v>0.15</v>
       </c>
       <c r="J65" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="K65" t="n">
-        <v>0.268</v>
+        <v>0.294</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R65" t="n">
-        <v>0.309</v>
+        <v>0.315</v>
       </c>
     </row>
   </sheetData>
@@ -4487,7 +4487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O483"/>
+  <dimension ref="A1:O482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33323,13 +33323,13 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>0.3545</v>
+        <v>0.3162</v>
       </c>
       <c r="F478" t="n">
-        <v>1.118375</v>
+        <v>1.116637</v>
       </c>
       <c r="G478" t="n">
-        <v>1.1158</v>
+        <v>1.542</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         </is>
       </c>
       <c r="L478" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
@@ -33386,13 +33386,13 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>0.2654</v>
+        <v>0.2245</v>
       </c>
       <c r="F479" t="n">
-        <v>1.155225</v>
+        <v>1.153469</v>
       </c>
       <c r="G479" t="n">
-        <v>0.9522</v>
+        <v>0.9888</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>0.5419</v>
+        <v>0.5538</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         </is>
       </c>
       <c r="L479" t="n">
-        <v>0.5419</v>
+        <v>0.5538</v>
       </c>
       <c r="M479" t="inlineStr">
         <is>
@@ -33449,13 +33449,13 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>0.324</v>
+        <v>0.3289</v>
       </c>
       <c r="F480" t="n">
-        <v>1.101101</v>
+        <v>1.098742</v>
       </c>
       <c r="G480" t="n">
-        <v>1.3748</v>
+        <v>0.8069</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         </is>
       </c>
       <c r="L480" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
@@ -33512,13 +33512,13 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>0.1526</v>
+        <v>0.2936</v>
       </c>
       <c r="F481" t="n">
-        <v>1.183489</v>
+        <v>1.141632</v>
       </c>
       <c r="G481" t="n">
-        <v>0.9885</v>
+        <v>1.4667</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>0.5202</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.5202</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -33575,13 +33575,13 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>0.2696</v>
+        <v>0.2154</v>
       </c>
       <c r="F482" t="n">
-        <v>1.124439</v>
+        <v>1.162918</v>
       </c>
       <c r="G482" t="n">
-        <v>0.9788</v>
+        <v>1.769</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>0.5376</v>
+        <v>0.6108</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         </is>
       </c>
       <c r="L482" t="n">
-        <v>0.5376</v>
+        <v>0.6108</v>
       </c>
       <c r="M482" t="inlineStr">
         <is>
@@ -33615,70 +33615,7 @@
         </is>
       </c>
       <c r="O482" t="n">
-        <v>0.0565</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>BHIA3</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E483" t="n">
-        <v>0.2355</v>
-      </c>
-      <c r="F483" t="n">
-        <v>1.120573</v>
-      </c>
-      <c r="G483" t="n">
-        <v>1.7661</v>
-      </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="I483" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J483" t="n">
-        <v>0.6065</v>
-      </c>
-      <c r="K483" t="inlineStr">
-        <is>
-          <t>RV_RANK</t>
-        </is>
-      </c>
-      <c r="L483" t="n">
-        <v>0.6065</v>
-      </c>
-      <c r="M483" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="N483" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="O483" t="n">
-        <v>0.6405</v>
+        <v>0.6505</v>
       </c>
     </row>
   </sheetData>
@@ -33874,13 +33811,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -33888,7 +33825,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="G7" t="n">
         <v>0.108</v>
@@ -34642,10 +34579,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.637</v>
+        <v>0.641</v>
       </c>
       <c r="G37" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="38">

--- a/saidas/historico_runs/historico_runs_2026_07_28.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_07_28.xlsx
@@ -4448,7 +4448,7 @@
         <v>0.65</v>
       </c>
       <c r="K65" t="n">
-        <v>0.294</v>
+        <v>0.225</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -33323,13 +33323,13 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>0.3162</v>
+        <v>0.3095</v>
       </c>
       <c r="F478" t="n">
-        <v>1.116637</v>
+        <v>1.103892</v>
       </c>
       <c r="G478" t="n">
-        <v>1.542</v>
+        <v>1.4762</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         </is>
       </c>
       <c r="L478" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         </is>
       </c>
       <c r="O478" t="n">
-        <v>0.245</v>
+        <v>0.2446</v>
       </c>
     </row>
     <row r="479">
@@ -33389,10 +33389,10 @@
         <v>0.2245</v>
       </c>
       <c r="F479" t="n">
-        <v>1.153469</v>
+        <v>1.146744</v>
       </c>
       <c r="G479" t="n">
-        <v>0.9888</v>
+        <v>0.9882</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>0.5538</v>
+        <v>0.5537</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         </is>
       </c>
       <c r="L479" t="n">
-        <v>0.5538</v>
+        <v>0.5537</v>
       </c>
       <c r="M479" t="inlineStr">
         <is>
@@ -33449,13 +33449,13 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>0.3289</v>
+        <v>0.3128</v>
       </c>
       <c r="F480" t="n">
-        <v>1.098742</v>
+        <v>1.107465</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8069</v>
+        <v>0.9059</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         </is>
       </c>
       <c r="L480" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
@@ -33512,13 +33512,13 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>0.2936</v>
+        <v>0.2226</v>
       </c>
       <c r="F481" t="n">
-        <v>1.141632</v>
+        <v>1.159549</v>
       </c>
       <c r="G481" t="n">
-        <v>1.4667</v>
+        <v>1.736</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
@@ -33578,10 +33578,10 @@
         <v>0.2154</v>
       </c>
       <c r="F482" t="n">
-        <v>1.162918</v>
+        <v>1.152624</v>
       </c>
       <c r="G482" t="n">
-        <v>1.769</v>
+        <v>1.7693</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>

--- a/saidas/historico_runs/historico_runs_2026_07_28.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_07_28.xlsx
@@ -4427,7 +4427,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -4436,25 +4436,25 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I65" t="n">
-        <v>0.15</v>
+        <v>0.093</v>
       </c>
       <c r="J65" t="n">
-        <v>0.65</v>
+        <v>0.653</v>
       </c>
       <c r="K65" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R65" t="n">
-        <v>0.315</v>
+        <v>0.321</v>
       </c>
     </row>
   </sheetData>
@@ -4487,7 +4487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O482"/>
+  <dimension ref="A1:O481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33323,13 +33323,13 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>0.3095</v>
+        <v>0.3076</v>
       </c>
       <c r="F478" t="n">
-        <v>1.103892</v>
+        <v>1.10471</v>
       </c>
       <c r="G478" t="n">
-        <v>1.4762</v>
+        <v>1.4416</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         </is>
       </c>
       <c r="L478" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         </is>
       </c>
       <c r="O478" t="n">
-        <v>0.2446</v>
+        <v>0.2444</v>
       </c>
     </row>
     <row r="479">
@@ -33386,13 +33386,13 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>0.2245</v>
+        <v>0.2293</v>
       </c>
       <c r="F479" t="n">
-        <v>1.146744</v>
+        <v>1.142491</v>
       </c>
       <c r="G479" t="n">
-        <v>0.9882</v>
+        <v>1.06</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>0.5537</v>
+        <v>0.5599</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         </is>
       </c>
       <c r="L479" t="n">
-        <v>0.5537</v>
+        <v>0.5599</v>
       </c>
       <c r="M479" t="inlineStr">
         <is>
@@ -33435,31 +33435,31 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>0.3128</v>
+        <v>0.2226</v>
       </c>
       <c r="F480" t="n">
-        <v>1.107465</v>
+        <v>1.159549</v>
       </c>
       <c r="G480" t="n">
-        <v>0.9059</v>
+        <v>1.7351</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -33468,28 +33468,28 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>0.5381</v>
+        <v>0.5809</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>RV_RANK</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="L480" t="n">
-        <v>0.5381</v>
+        <v>0.5809</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Sem estrutura com edge positivo — não operar</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="O480" t="n">
-        <v>0.1501</v>
+        <v>-0.1354</v>
       </c>
     </row>
     <row r="481">
@@ -33498,31 +33498,31 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>0.2226</v>
+        <v>0.2112</v>
       </c>
       <c r="F481" t="n">
-        <v>1.159549</v>
+        <v>1.154009</v>
       </c>
       <c r="G481" t="n">
-        <v>1.736</v>
+        <v>1.9402</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>aprovado_executor_nivel_A</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -33531,91 +33531,28 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>0.581</v>
+        <v>0.6287</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>RV_RANK</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.581</v>
+        <v>0.6287</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Sem estrutura com edge positivo — não operar</t>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="O481" t="n">
-        <v>-0.1354</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>BHIA3</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E482" t="n">
-        <v>0.2154</v>
-      </c>
-      <c r="F482" t="n">
-        <v>1.152624</v>
-      </c>
-      <c r="G482" t="n">
-        <v>1.7693</v>
-      </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="I482" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J482" t="n">
-        <v>0.6108</v>
-      </c>
-      <c r="K482" t="inlineStr">
-        <is>
-          <t>RV_RANK</t>
-        </is>
-      </c>
-      <c r="L482" t="n">
-        <v>0.6108</v>
-      </c>
-      <c r="M482" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="N482" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="O482" t="n">
-        <v>0.6505</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -33699,55 +33636,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT, Compra CALL, Monitorar CALL, Monitorar PUT</t>
+          <t>Alerta CALL, Alerta PUT, Compra PUT, Monitorar CALL, Monitorar PUT</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.143</v>
+        <v>0.075</v>
       </c>
       <c r="G3" t="n">
-        <v>0.15</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PETR3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>32</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT, Compra PUT, Monitorar CALL, Monitorar PUT</t>
+          <t>Alerta CALL, Alerta PUT, Compra CALL, Monitorar CALL, Monitorar PUT</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.075</v>
+        <v>0.142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.172</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -34582,7 +34519,7 @@
         <v>0.641</v>
       </c>
       <c r="G37" t="n">
-        <v>0.65</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="38">
